--- a/macro/양식/임시중단_강제종료_양식.xlsx
+++ b/macro/양식/임시중단_강제종료_양식.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -478,11 +478,6 @@
           <t>강제종료</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>메모</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -490,7 +485,11 @@
           <t>1839711962</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr"/>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>P2116A864DC2B0CF2</t>
+        </is>
+      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>O</t>
@@ -499,11 +498,6 @@
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>O</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>예: MID 전체 캠페인 임시중단</t>
         </is>
       </c>
     </row>

--- a/macro/양식/임시중단_강제종료_양식.xlsx
+++ b/macro/양식/임시중단_강제종료_양식.xlsx
@@ -447,10 +447,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -460,20 +460,25 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>영업점</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Pcode</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>임시중단B</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>강제종료</t>
         </is>
@@ -482,20 +487,25 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>1839711962</t>
+          <t>제이솔컴퍼니</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>1230085864</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>P2116A864DC2B0CF2</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>O</t>
         </is>
